--- a/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0035.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0035.xlsx
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Mở khóa bằng cách hoàn thành các nhiệm vụ Moon-Chasing Festival</t>
+          <t>Mở khóa bằng cách hoàn thành các nhiệm vụ Lễ Hội Đuổi Trăng</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Hoàn thành "Silent as a Falling Leaf" để có trải nghiệm tốt hơn</t>
+          <t>Hoàn thành "Lặng Như Lá Rơi" để có trải nghiệm tốt hơn</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Tutorial Sự Kiện để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn Sự Kiện để mở khóa</t>
         </is>
       </c>
     </row>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Nhiệm vụ hàng ngày</t>
+          <t>Nhiệm Vụ Hằng Ngày</t>
         </is>
       </c>
     </row>
@@ -28463,7 +28463,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Nhiệm vụ mới</t>
+          <t>Nhiệm Vụ Mới</t>
         </is>
       </c>
     </row>
